--- a/data/FY24Q4.xlsx
+++ b/data/FY24Q4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/Downloads/123/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952C9301-E966-A44C-A1A6-CF3B83DB23CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DA2BA6-0E7B-9E48-8C93-843799424794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10900" yWindow="2920" windowWidth="26640" windowHeight="15320" xr2:uid="{8B96DD09-AD88-7743-92B9-2B296BF94682}"/>
+    <workbookView xWindow="7560" yWindow="2920" windowWidth="26640" windowHeight="15320" xr2:uid="{8B96DD09-AD88-7743-92B9-2B296BF94682}"/>
   </bookViews>
   <sheets>
     <sheet name="24Q4" sheetId="2" r:id="rId1"/>
@@ -1662,7 +1662,7 @@
         <v>45</v>
       </c>
       <c r="C6" s="12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="33"/>
@@ -1673,11 +1673,11 @@
         <v>45</v>
       </c>
       <c r="K6" s="12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L6" s="14"/>
       <c r="M6" s="12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N6" s="14">
         <v>0</v>
@@ -1690,11 +1690,11 @@
         <v>45</v>
       </c>
       <c r="S6" s="12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T6" s="14"/>
       <c r="U6" s="12">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="V6" s="14">
         <v>0</v>
@@ -1707,11 +1707,11 @@
         <v>45</v>
       </c>
       <c r="AA6" s="12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB6" s="14"/>
       <c r="AC6" s="12">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AD6" s="14">
         <v>0</v>
@@ -1724,11 +1724,11 @@
         <v>45</v>
       </c>
       <c r="AI6" s="12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ6" s="14"/>
       <c r="AK6" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL6" s="14">
         <v>0</v>
@@ -1741,11 +1741,11 @@
         <v>45</v>
       </c>
       <c r="AQ6" s="12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR6" s="14"/>
       <c r="AS6" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT6" s="14">
         <v>0</v>
@@ -1758,11 +1758,11 @@
         <v>45</v>
       </c>
       <c r="AY6" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ6" s="14"/>
       <c r="BA6" s="12">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="BB6" s="14">
         <v>0</v>
@@ -1775,11 +1775,11 @@
         <v>45</v>
       </c>
       <c r="BG6" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH6" s="14"/>
       <c r="BI6" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ6" s="14">
         <v>0</v>
@@ -1792,11 +1792,11 @@
         <v>45</v>
       </c>
       <c r="BO6" s="12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BP6" s="14"/>
       <c r="BQ6" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR6" s="14">
         <v>0</v>
@@ -1809,11 +1809,11 @@
         <v>45</v>
       </c>
       <c r="BW6" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX6" s="14"/>
       <c r="BY6" s="12">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BZ6" s="14">
         <v>0</v>
@@ -1826,11 +1826,11 @@
         <v>45</v>
       </c>
       <c r="CE6" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CF6" s="14"/>
       <c r="CG6" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH6" s="14">
         <v>0</v>
@@ -1843,11 +1843,11 @@
         <v>45</v>
       </c>
       <c r="CM6" s="12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CN6" s="14"/>
       <c r="CO6" s="12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="CP6" s="14">
         <v>0</v>
@@ -1860,11 +1860,11 @@
         <v>45</v>
       </c>
       <c r="CU6" s="27">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="CV6" s="28"/>
       <c r="CW6" s="12">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="CX6" s="14">
         <v>0</v>
@@ -4622,7 +4622,7 @@
         <v>45</v>
       </c>
       <c r="C18" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D18" s="34"/>
       <c r="F18" s="34"/>
@@ -4632,11 +4632,11 @@
         <v>45</v>
       </c>
       <c r="K18" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" s="34"/>
       <c r="M18" s="12">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="N18" s="14">
         <v>0</v>
@@ -4649,11 +4649,11 @@
         <v>45</v>
       </c>
       <c r="S18" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T18" s="34"/>
       <c r="U18" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V18" s="14">
         <v>0</v>
@@ -4666,7 +4666,7 @@
         <v>45</v>
       </c>
       <c r="AA18" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB18" s="34"/>
       <c r="AC18" s="12">
@@ -4683,11 +4683,11 @@
         <v>45</v>
       </c>
       <c r="AI18" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ18" s="34"/>
       <c r="AK18" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL18" s="14">
         <v>0</v>
@@ -4700,11 +4700,11 @@
         <v>45</v>
       </c>
       <c r="AQ18" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AR18" s="34"/>
       <c r="AS18" s="12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT18" s="14">
         <v>0</v>
@@ -4717,11 +4717,11 @@
         <v>45</v>
       </c>
       <c r="AY18" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AZ18" s="34"/>
       <c r="BA18" s="12">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BB18" s="14">
         <v>0</v>
@@ -4734,7 +4734,7 @@
         <v>45</v>
       </c>
       <c r="BG18" s="35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH18" s="36"/>
       <c r="BI18" s="12">
@@ -4752,11 +4752,11 @@
         <v>45</v>
       </c>
       <c r="BO18" s="35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BP18" s="36"/>
       <c r="BQ18" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BR18" s="14">
         <v>0</v>
@@ -4769,7 +4769,7 @@
         <v>45</v>
       </c>
       <c r="BW18" s="35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BX18" s="36"/>
       <c r="BY18" s="12">
@@ -4786,7 +4786,7 @@
         <v>45</v>
       </c>
       <c r="CE18" s="35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CF18" s="36"/>
       <c r="CG18" s="12">
@@ -4803,11 +4803,11 @@
         <v>45</v>
       </c>
       <c r="CM18" s="35">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CN18" s="36"/>
       <c r="CO18" s="12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="CP18" s="14">
         <v>0</v>
@@ -4820,11 +4820,11 @@
         <v>45</v>
       </c>
       <c r="CU18" s="35">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="CV18" s="36"/>
       <c r="CW18" s="12">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="CX18" s="14">
         <v>0</v>
@@ -7582,7 +7582,7 @@
         <v>45</v>
       </c>
       <c r="C30" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D30" s="34"/>
       <c r="F30" s="34"/>
@@ -7592,7 +7592,7 @@
         <v>45</v>
       </c>
       <c r="K30" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="34"/>
       <c r="M30" s="12">
@@ -7609,11 +7609,11 @@
         <v>45</v>
       </c>
       <c r="S30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" s="34"/>
       <c r="U30" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V30" s="14">
         <v>0</v>
@@ -7626,7 +7626,7 @@
         <v>45</v>
       </c>
       <c r="AA30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" s="34"/>
       <c r="AC30" s="12">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AJ30" s="34"/>
       <c r="AK30" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL30" s="14">
         <v>0</v>
@@ -7660,11 +7660,11 @@
         <v>45</v>
       </c>
       <c r="AQ30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR30" s="34"/>
       <c r="AS30" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT30" s="14">
         <v>0</v>
@@ -7677,11 +7677,11 @@
         <v>45</v>
       </c>
       <c r="AY30" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ30" s="34"/>
       <c r="BA30" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB30" s="14">
         <v>0</v>
@@ -7694,11 +7694,11 @@
         <v>45</v>
       </c>
       <c r="BG30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH30" s="34"/>
       <c r="BI30" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BJ30" s="14">
         <v>0</v>
@@ -7712,11 +7712,11 @@
         <v>45</v>
       </c>
       <c r="BO30" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP30" s="34"/>
       <c r="BQ30" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR30" s="14">
         <v>0</v>
@@ -7733,7 +7733,7 @@
       </c>
       <c r="BX30" s="34"/>
       <c r="BY30" s="12">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BZ30" s="14">
         <v>0</v>
@@ -7746,11 +7746,11 @@
         <v>45</v>
       </c>
       <c r="CE30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF30" s="34"/>
       <c r="CG30" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH30" s="14">
         <v>0</v>
@@ -7763,11 +7763,11 @@
         <v>45</v>
       </c>
       <c r="CM30" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CN30" s="34"/>
       <c r="CO30" s="12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CP30" s="14">
         <v>0</v>
@@ -7780,11 +7780,11 @@
         <v>45</v>
       </c>
       <c r="CU30" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CV30" s="34"/>
       <c r="CW30" s="12">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="CX30" s="14">
         <v>0</v>
@@ -10542,7 +10542,7 @@
         <v>45</v>
       </c>
       <c r="C42" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D42" s="34"/>
       <c r="F42" s="34"/>
@@ -10552,7 +10552,7 @@
         <v>45</v>
       </c>
       <c r="K42" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="34"/>
       <c r="M42" s="12">
@@ -10569,11 +10569,11 @@
         <v>45</v>
       </c>
       <c r="S42" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T42" s="34"/>
       <c r="U42" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="14">
         <v>0</v>
@@ -10586,11 +10586,11 @@
         <v>45</v>
       </c>
       <c r="AA42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB42" s="34"/>
       <c r="AC42" s="12">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AD42" s="14">
         <v>0</v>
@@ -10603,7 +10603,7 @@
         <v>45</v>
       </c>
       <c r="AI42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ42" s="34"/>
       <c r="AK42" s="12">
@@ -10620,11 +10620,11 @@
         <v>45</v>
       </c>
       <c r="AQ42" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AR42" s="34"/>
       <c r="AS42" s="12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT42" s="14">
         <v>0</v>
@@ -10637,11 +10637,11 @@
         <v>45</v>
       </c>
       <c r="AY42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ42" s="34"/>
       <c r="BA42" s="12">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BB42" s="14">
         <v>0</v>
@@ -10658,7 +10658,7 @@
       </c>
       <c r="BH42" s="34"/>
       <c r="BI42" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BJ42" s="14">
         <v>0</v>
@@ -10672,11 +10672,11 @@
         <v>45</v>
       </c>
       <c r="BO42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP42" s="34"/>
       <c r="BQ42" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR42" s="14">
         <v>0</v>
@@ -10693,7 +10693,7 @@
       </c>
       <c r="BX42" s="34"/>
       <c r="BY42" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BZ42" s="14">
         <v>0</v>
@@ -10723,11 +10723,11 @@
         <v>45</v>
       </c>
       <c r="CM42" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CN42" s="34"/>
       <c r="CO42" s="12">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CP42" s="14">
         <v>0</v>
@@ -10740,11 +10740,11 @@
         <v>45</v>
       </c>
       <c r="CU42" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CV42" s="34"/>
       <c r="CW42" s="12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CX42" s="14">
         <v>0</v>
